--- a/bin/Debug/Template/ReciveIssueImport.xlsx
+++ b/bin/Debug/Template/ReciveIssueImport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDCBCAE-B98D-4E60-865B-0539A30E4F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95962367-00AF-4BFF-8991-9EB586A56A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0000"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -90,10 +87,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -407,6 +405,9 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
